--- a/Signale.xlsx
+++ b/Signale.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Christof\Projects\Python\App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D76CEC3A-4505-4F23-BF9E-A44A62BE1E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5EE1FF9-D69E-45DA-9DDA-7027CA4058D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13276" xr2:uid="{BBD6C58D-68A4-4BB0-9DED-4FB51D210800}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
   <si>
     <t>BackendEvents</t>
   </si>
@@ -50,16 +50,103 @@
     <t>BackendSetup</t>
   </si>
   <si>
-    <t>newGraph(var name, var color);</t>
-  </si>
-  <si>
-    <t>scrollRight(var pixel);</t>
-  </si>
-  <si>
-    <t>com_port_update(var portList);</t>
-  </si>
-  <si>
-    <t>ui_setup(var settings)</t>
+    <t>connect()</t>
+  </si>
+  <si>
+    <t>is_connected()</t>
+  </si>
+  <si>
+    <t>set_plot_area(area)</t>
+  </si>
+  <si>
+    <t>add_graph(name,graph)</t>
+  </si>
+  <si>
+    <t>set_axis(xAxis, yAxis)</t>
+  </si>
+  <si>
+    <t>ui_setup(ui_settings)</t>
+  </si>
+  <si>
+    <t>QML Backend</t>
+  </si>
+  <si>
+    <t>Python Backend</t>
+  </si>
+  <si>
+    <t>Setup</t>
+  </si>
+  <si>
+    <t>backend_setup_done_changed</t>
+  </si>
+  <si>
+    <t>ui_setup</t>
+  </si>
+  <si>
+    <t>ui_setup_done_changed</t>
+  </si>
+  <si>
+    <t>Settings</t>
+  </si>
+  <si>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>var name, var color</t>
+  </si>
+  <si>
+    <t>newGraph</t>
+  </si>
+  <si>
+    <t>var pixel</t>
+  </si>
+  <si>
+    <t>var portList</t>
+  </si>
+  <si>
+    <t>var settings</t>
+  </si>
+  <si>
+    <t>scrollRight</t>
+  </si>
+  <si>
+    <t>com_port_update</t>
+  </si>
+  <si>
+    <t xml:space="preserve">set_settings </t>
+  </si>
+  <si>
+    <t>interface_type, settings</t>
+  </si>
+  <si>
+    <t>get_settings</t>
+  </si>
+  <si>
+    <t>interface_type</t>
+  </si>
+  <si>
+    <t>settings_valid</t>
+  </si>
+  <si>
+    <t>area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name. Graph </t>
+  </si>
+  <si>
+    <t>xAxis, yAxis</t>
+  </si>
+  <si>
+    <t>ui_settings</t>
+  </si>
+  <si>
+    <t>Qvariant settings</t>
+  </si>
+  <si>
+    <t>bool status</t>
+  </si>
+  <si>
+    <t>Python</t>
   </si>
 </sst>
 </file>
@@ -95,8 +182,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -411,54 +502,201 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D556CD9F-3B4C-47D0-8E8C-DD37D3D3B90B}">
-  <dimension ref="G9:H24"/>
+  <dimension ref="A8:I31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
+    <col min="3" max="3" width="16.1328125" customWidth="1"/>
+    <col min="4" max="4" width="25.06640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.19921875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.06640625" customWidth="1"/>
-    <col min="8" max="8" width="27.73046875" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="7:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="G8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
       <c r="G9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="7:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="G10" t="s">
+        <v>17</v>
+      </c>
       <c r="H10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="7:8" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+      <c r="I10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" t="s">
+        <v>17</v>
+      </c>
       <c r="H11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="7:8" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+      <c r="I11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" t="s">
+        <v>17</v>
+      </c>
       <c r="H12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="7:8" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+      <c r="I12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" t="s">
+        <v>17</v>
+      </c>
       <c r="H13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="7:8" x14ac:dyDescent="0.45">
+        <v>14</v>
+      </c>
+      <c r="I13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="G15" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="C16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="7:9" x14ac:dyDescent="0.45">
       <c r="G20" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="7:7" x14ac:dyDescent="0.45">
-      <c r="G24" t="s">
+    <row r="21" spans="7:9" x14ac:dyDescent="0.45">
+      <c r="H21" t="s">
+        <v>25</v>
+      </c>
+      <c r="I21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="7:9" x14ac:dyDescent="0.45">
+      <c r="H22" t="s">
+        <v>27</v>
+      </c>
+      <c r="I22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="7:9" x14ac:dyDescent="0.45">
+      <c r="H23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="7:9" x14ac:dyDescent="0.45">
+      <c r="H24" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="7:9" x14ac:dyDescent="0.45">
+      <c r="H25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="7:9" x14ac:dyDescent="0.45">
+      <c r="H26" t="s">
+        <v>6</v>
+      </c>
+      <c r="I26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="7:9" x14ac:dyDescent="0.45">
+      <c r="H27" t="s">
+        <v>7</v>
+      </c>
+      <c r="I27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="7:9" x14ac:dyDescent="0.45">
+      <c r="H28" t="s">
+        <v>8</v>
+      </c>
+      <c r="I28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="7:9" x14ac:dyDescent="0.45">
+      <c r="G30" t="s">
         <v>3</v>
       </c>
     </row>
+    <row r="31" spans="7:9" x14ac:dyDescent="0.45">
+      <c r="H31" t="s">
+        <v>9</v>
+      </c>
+      <c r="I31" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="G8:I8"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>